--- a/datasets/scenario.xlsx
+++ b/datasets/scenario.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajay\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitContent\GenAI_DataBricks_GoogleCloud\GenAI_DataBricks_GoogleCloud\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,12 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="3">
   <si>
     <t>cat follows dog in our company</t>
   </si>
   <si>
     <t>cat follows dog in our society</t>
+  </si>
+  <si>
+    <t>cat follows dog at night in our society</t>
   </si>
 </sst>
 </file>
@@ -347,7 +350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.08984375" customWidth="1"/>
@@ -383,6 +386,16 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
